--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -415,7 +415,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-08T07:58:53Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-08T10:50:35Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -415,7 +415,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-08T10:50:35Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-15T08:47:24Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -17,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-es-ES]#,##0"/>
+    <numFmt numFmtId="165" formatCode="[$-es-ES]#,##0.00"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -69,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,6 +86,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -114,6 +123,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -144,6 +156,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -507,10 +522,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="7" t="n">
         <v>2008</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="8" t="n">
         <v>3.276408308619679</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -540,10 +555,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="7" t="n">
         <v>2009</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="8" t="n">
         <v>-4.095858699654258</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -573,10 +588,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="7" t="n">
         <v>2010</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="8" t="n">
         <v>-0.6620080132279327</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -606,10 +621,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="7" t="n">
         <v>2011</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="8" t="n">
         <v>2.728942883695225</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -639,10 +654,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="7" t="n">
         <v>2012</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="8" t="n">
         <v>4.243300030305591</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -672,10 +687,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="7" t="n">
         <v>2013</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="8" t="n">
         <v>0.07771331367443679</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -705,10 +720,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="7" t="n">
         <v>2014</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="8" t="n">
         <v>-2.305807182523338</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -738,10 +753,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="7" t="n">
         <v>2015</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="8" t="n">
         <v>-3.868720967947553</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -771,10 +786,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="7" t="n">
         <v>2016</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="8" t="n">
         <v>-16.97801742690727</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -804,10 +819,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="7" t="n">
         <v>2017</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="8" t="n">
         <v>-14.42010721738242</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -837,10 +852,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="7" t="n">
         <v>2018</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="8" t="n">
         <v>-21.39586857963141</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -870,10 +885,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="7" t="n">
         <v>2019</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="8" t="n">
         <v>-28.99145829523422</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -903,10 +918,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="7" t="n">
         <v>2020</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="8" t="n">
         <v>-33.20381272402878</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -936,10 +951,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="7" t="n">
         <v>2021</v>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="8" t="n">
         <v>1.111016250264043</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -969,10 +984,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="7" t="n">
         <v>2022</v>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="8" t="n">
         <v>14.91768022765017</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1002,10 +1017,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="8" t="n">
         <v>5.143618581513593</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1035,10 +1050,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="7" t="n">
         <v>2024</v>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="8" t="n">
         <v>9.025539143402</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1068,10 +1083,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="8" t="n">
         <v>8.944487326024571</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1238,7 +1253,7 @@
           <t>first_year</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="7" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1248,7 +1263,7 @@
           <t>last_year</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="7" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -1258,7 +1273,7 @@
           <t>records</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="7" t="n">
         <v>18</v>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -487,37 +487,37 @@
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>Año</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>annual_real_gdp_growth_pct</t>
+          <t>Crecimiento anual PIB real (%)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>Unidad</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>Frecuencia</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>Fuente</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>source_url</t>
+          <t>URL fuente</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>fetched_at</t>
+          <t>Fecha de captura</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -79,6 +79,12 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -86,22 +92,84 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -116,16 +184,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -134,7 +199,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -149,16 +214,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -522,596 +584,596 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="4" t="n">
         <v>2008</v>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="5" t="n">
         <v>3.276408308619679</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Variación porcentual anual a precios de 2007</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Banco Central de Venezuela</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-15T09:36:47Z</t>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Variación porcentual anual a precios de 2007</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="4" t="n">
         <v>2009</v>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="5" t="n">
         <v>-4.095858699654258</v>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Variación porcentual anual a precios de 2007</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Banco Central de Venezuela</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-15T09:36:47Z</t>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Variación porcentual anual a precios de 2007</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="4" t="n">
         <v>2010</v>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="5" t="n">
         <v>-0.6620080132279327</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Variación porcentual anual a precios de 2007</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Banco Central de Venezuela</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-15T09:36:47Z</t>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Variación porcentual anual a precios de 2007</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="4" t="n">
         <v>2011</v>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="5" t="n">
         <v>2.728942883695225</v>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Variación porcentual anual a precios de 2007</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Banco Central de Venezuela</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-15T09:36:47Z</t>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Variación porcentual anual a precios de 2007</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="4" t="n">
         <v>2012</v>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="5" t="n">
         <v>4.243300030305591</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Variación porcentual anual a precios de 2007</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Banco Central de Venezuela</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-15T09:36:47Z</t>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Variación porcentual anual a precios de 2007</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="4" t="n">
         <v>2013</v>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="5" t="n">
         <v>0.07771331367443679</v>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Variación porcentual anual a precios de 2007</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Banco Central de Venezuela</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-15T09:36:47Z</t>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Variación porcentual anual a precios de 2007</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="4" t="n">
         <v>2014</v>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="5" t="n">
         <v>-2.305807182523338</v>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Variación porcentual anual a precios de 2007</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Banco Central de Venezuela</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-15T09:36:47Z</t>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Variación porcentual anual a precios de 2007</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="5" t="n">
         <v>-3.868720967947553</v>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Variación porcentual anual a precios de 2007</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Banco Central de Venezuela</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-15T09:36:47Z</t>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Variación porcentual anual a precios de 2007</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="4" t="n">
         <v>2016</v>
       </c>
-      <c r="B15" s="8" t="n">
+      <c r="B15" s="5" t="n">
         <v>-16.97801742690727</v>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Variación porcentual anual a precios de 2007</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Banco Central de Venezuela</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-15T09:36:47Z</t>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Variación porcentual anual a precios de 2007</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="4" t="n">
         <v>2017</v>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B16" s="5" t="n">
         <v>-14.42010721738242</v>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Variación porcentual anual a precios de 2007</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Banco Central de Venezuela</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-15T09:36:47Z</t>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Variación porcentual anual a precios de 2007</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="4" t="n">
         <v>2018</v>
       </c>
-      <c r="B17" s="8" t="n">
+      <c r="B17" s="5" t="n">
         <v>-21.39586857963141</v>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Variación porcentual anual a precios de 2007</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Banco Central de Venezuela</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-15T09:36:47Z</t>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Variación porcentual anual a precios de 2007</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="4" t="n">
         <v>2019</v>
       </c>
-      <c r="B18" s="8" t="n">
+      <c r="B18" s="5" t="n">
         <v>-28.99145829523422</v>
       </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Variación porcentual anual a precios de 2007</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Banco Central de Venezuela</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-15T09:36:47Z</t>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Variación porcentual anual a precios de 2007</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="4" t="n">
         <v>2020</v>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B19" s="5" t="n">
         <v>-33.20381272402878</v>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Variación porcentual anual a precios de 2007</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Banco Central de Venezuela</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-15T09:36:47Z</t>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Variación porcentual anual a precios de 2007</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="4" t="n">
         <v>2021</v>
       </c>
-      <c r="B20" s="8" t="n">
+      <c r="B20" s="5" t="n">
         <v>1.111016250264043</v>
       </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Variación porcentual anual a precios de 2007</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Banco Central de Venezuela</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-15T09:36:47Z</t>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Variación porcentual anual a precios de 2007</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="4" t="n">
         <v>2022</v>
       </c>
-      <c r="B21" s="8" t="n">
+      <c r="B21" s="5" t="n">
         <v>14.91768022765017</v>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Variación porcentual anual a precios de 2007</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Banco Central de Venezuela</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-15T09:36:47Z</t>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Variación porcentual anual a precios de 2007</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="4" t="n">
         <v>2023</v>
       </c>
-      <c r="B22" s="8" t="n">
+      <c r="B22" s="5" t="n">
         <v>5.143618581513593</v>
       </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Variación porcentual anual a precios de 2007</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Banco Central de Venezuela</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-15T09:36:47Z</t>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Variación porcentual anual a precios de 2007</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="4" t="n">
         <v>2024</v>
       </c>
-      <c r="B23" s="8" t="n">
+      <c r="B23" s="5" t="n">
         <v>9.025539143402</v>
       </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Variación porcentual anual a precios de 2007</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Banco Central de Venezuela</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-15T09:36:47Z</t>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Variación porcentual anual a precios de 2007</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="B24" s="8" t="n">
+      <c r="B24" s="5" t="n">
         <v>8.944487326024571</v>
       </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Variación porcentual anual a precios de 2007</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Banco Central de Venezuela</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-15T09:36:47Z</t>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Variación porcentual anual a precios de 2007</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -1152,150 +1214,150 @@
     <row r="4" ht="16" customHeight="1"/>
     <row r="5" ht="8" customHeight="1"/>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Campo</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>dataset_id</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>bcv_pib_real_anual</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Producto interno bruto real anual</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Banco Central de Venezuela</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>source_url</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>official_source</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>last_fetched_at</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-15T09:36:47Z</t>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>first_year</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="4" t="n">
         <v>2008</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>last_year</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="4" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>records</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B16" s="4" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-15T09:36:47Z"}</t>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-17T14:53:24Z"}</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Crecimiento anual del PIB real total normalizado desde workbook oficial BCV 5_2_1_si_anual.xlsx.</t>
         </is>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-17T14:53:24Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-22T15:17:10Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-22T15:17:10Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-22T21:35:44Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-22T21:35:44Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-23T21:35:02Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-23T21:35:02Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-24T21:36:07Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-24T21:36:07Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-25T21:23:56Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-25T21:23:56Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-26T21:25:45Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-26T21:25:45Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-27T21:37:27Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-27T21:37:27Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-28T21:37:46Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-28T21:37:46Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-29T21:26:21Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-29T21:26:21Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-30T21:40:54Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-30T21:40:54Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-31T21:36:45Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-07-31T21:36:45Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-01T21:23:56Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-01T21:23:56Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-02T14:43:05Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-02T14:43:05Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-02T21:23:57Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-02T21:23:57Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-03T21:38:52Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-03T21:38:52Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-04T21:47:54Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-04T21:47:54Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-05T21:44:20Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-05T21:44:20Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-07T00:56:55Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-07T00:56:55Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-07T14:18:54Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-07T14:18:54Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-07T21:09:09Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-07T21:09:09Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-08T20:57:47Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-08T20:57:47Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-09T21:02:01Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-09T21:02:01Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-10T21:11:05Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-10T21:11:05Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-11T21:14:58Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-11T21:14:58Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-12T14:32:11Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-12T14:32:11Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-12T21:12:47Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-12T21:12:47Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-13T21:12:32Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-13T21:12:32Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-14T20:55:15Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-14T20:55:15Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-15T20:47:07Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-15T20:47:07Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-16T20:46:07Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-16T20:46:07Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-17T13:52:15Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-17T13:52:15Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-17T20:52:46Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
         <v>2022</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>14.91768022765017</v>
+        <v>15.10310995712332</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
         <v>2023</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>5.143618581513593</v>
+        <v>5.690099636766604</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
         <v>2024</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>9.025539143402</v>
+        <v>8.881616545123563</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
         <v>2025</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>8.944487326024571</v>
+        <v>9.012862992888856</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 8.944487326024571, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-17T20:52:46Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-21T16:34:23Z"}</t>
         </is>
       </c>
     </row>
@@ -1360,6 +1360,18 @@
       <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Crecimiento anual del PIB real total normalizado desde workbook oficial BCV 5_2_1_si_anual.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>source_sheet</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Var_pun%</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:23Z</t>
+          <t>2026-08-21T20:49:32Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:23Z</t>
+          <t>2026-08-21T20:49:32Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:23Z</t>
+          <t>2026-08-21T20:49:32Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:23Z</t>
+          <t>2026-08-21T20:49:32Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:23Z</t>
+          <t>2026-08-21T20:49:32Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:23Z</t>
+          <t>2026-08-21T20:49:32Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:23Z</t>
+          <t>2026-08-21T20:49:32Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:23Z</t>
+          <t>2026-08-21T20:49:32Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:23Z</t>
+          <t>2026-08-21T20:49:32Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:23Z</t>
+          <t>2026-08-21T20:49:32Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:23Z</t>
+          <t>2026-08-21T20:49:32Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:23Z</t>
+          <t>2026-08-21T20:49:32Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:23Z</t>
+          <t>2026-08-21T20:49:32Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:23Z</t>
+          <t>2026-08-21T20:49:32Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:23Z</t>
+          <t>2026-08-21T20:49:32Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:23Z</t>
+          <t>2026-08-21T20:49:32Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:23Z</t>
+          <t>2026-08-21T20:49:32Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:23Z</t>
+          <t>2026-08-21T20:49:32Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:23Z</t>
+          <t>2026-08-21T20:49:32Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-21T16:34:23Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-21T20:49:32Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:32Z</t>
+          <t>2026-08-22T13:43:42Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:32Z</t>
+          <t>2026-08-22T13:43:42Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:32Z</t>
+          <t>2026-08-22T13:43:42Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:32Z</t>
+          <t>2026-08-22T13:43:42Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:32Z</t>
+          <t>2026-08-22T13:43:42Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:32Z</t>
+          <t>2026-08-22T13:43:42Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:32Z</t>
+          <t>2026-08-22T13:43:42Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:32Z</t>
+          <t>2026-08-22T13:43:42Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:32Z</t>
+          <t>2026-08-22T13:43:42Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:32Z</t>
+          <t>2026-08-22T13:43:42Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:32Z</t>
+          <t>2026-08-22T13:43:42Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:32Z</t>
+          <t>2026-08-22T13:43:42Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:32Z</t>
+          <t>2026-08-22T13:43:42Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:32Z</t>
+          <t>2026-08-22T13:43:42Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:32Z</t>
+          <t>2026-08-22T13:43:42Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:32Z</t>
+          <t>2026-08-22T13:43:42Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:32Z</t>
+          <t>2026-08-22T13:43:42Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:32Z</t>
+          <t>2026-08-22T13:43:42Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:32Z</t>
+          <t>2026-08-22T13:43:42Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-21T20:49:32Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-22T13:43:42Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:42Z</t>
+          <t>2026-08-22T20:47:44Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:42Z</t>
+          <t>2026-08-22T20:47:44Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:42Z</t>
+          <t>2026-08-22T20:47:44Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:42Z</t>
+          <t>2026-08-22T20:47:44Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:42Z</t>
+          <t>2026-08-22T20:47:44Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:42Z</t>
+          <t>2026-08-22T20:47:44Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:42Z</t>
+          <t>2026-08-22T20:47:44Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:42Z</t>
+          <t>2026-08-22T20:47:44Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:42Z</t>
+          <t>2026-08-22T20:47:44Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:42Z</t>
+          <t>2026-08-22T20:47:44Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:42Z</t>
+          <t>2026-08-22T20:47:44Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:42Z</t>
+          <t>2026-08-22T20:47:44Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:42Z</t>
+          <t>2026-08-22T20:47:44Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:42Z</t>
+          <t>2026-08-22T20:47:44Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:42Z</t>
+          <t>2026-08-22T20:47:44Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:42Z</t>
+          <t>2026-08-22T20:47:44Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:42Z</t>
+          <t>2026-08-22T20:47:44Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:42Z</t>
+          <t>2026-08-22T20:47:44Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:42Z</t>
+          <t>2026-08-22T20:47:44Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-22T13:43:42Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-22T20:47:44Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:44Z</t>
+          <t>2026-08-23T20:47:27Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:44Z</t>
+          <t>2026-08-23T20:47:27Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:44Z</t>
+          <t>2026-08-23T20:47:27Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:44Z</t>
+          <t>2026-08-23T20:47:27Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:44Z</t>
+          <t>2026-08-23T20:47:27Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:44Z</t>
+          <t>2026-08-23T20:47:27Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:44Z</t>
+          <t>2026-08-23T20:47:27Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:44Z</t>
+          <t>2026-08-23T20:47:27Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:44Z</t>
+          <t>2026-08-23T20:47:27Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:44Z</t>
+          <t>2026-08-23T20:47:27Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:44Z</t>
+          <t>2026-08-23T20:47:27Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:44Z</t>
+          <t>2026-08-23T20:47:27Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:44Z</t>
+          <t>2026-08-23T20:47:27Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:44Z</t>
+          <t>2026-08-23T20:47:27Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:44Z</t>
+          <t>2026-08-23T20:47:27Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:44Z</t>
+          <t>2026-08-23T20:47:27Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:44Z</t>
+          <t>2026-08-23T20:47:27Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:44Z</t>
+          <t>2026-08-23T20:47:27Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:44Z</t>
+          <t>2026-08-23T20:47:27Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-22T20:47:44Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-23T20:47:27Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:27Z</t>
+          <t>2026-08-24T20:57:42Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:27Z</t>
+          <t>2026-08-24T20:57:42Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:27Z</t>
+          <t>2026-08-24T20:57:42Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:27Z</t>
+          <t>2026-08-24T20:57:42Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:27Z</t>
+          <t>2026-08-24T20:57:42Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:27Z</t>
+          <t>2026-08-24T20:57:42Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:27Z</t>
+          <t>2026-08-24T20:57:42Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:27Z</t>
+          <t>2026-08-24T20:57:42Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:27Z</t>
+          <t>2026-08-24T20:57:42Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:27Z</t>
+          <t>2026-08-24T20:57:42Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:27Z</t>
+          <t>2026-08-24T20:57:42Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:27Z</t>
+          <t>2026-08-24T20:57:42Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:27Z</t>
+          <t>2026-08-24T20:57:42Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:27Z</t>
+          <t>2026-08-24T20:57:42Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:27Z</t>
+          <t>2026-08-24T20:57:42Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:27Z</t>
+          <t>2026-08-24T20:57:42Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:27Z</t>
+          <t>2026-08-24T20:57:42Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:27Z</t>
+          <t>2026-08-24T20:57:42Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:27Z</t>
+          <t>2026-08-24T20:57:42Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-23T20:47:27Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-24T20:57:42Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:42Z</t>
+          <t>2026-08-25T20:55:01Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:42Z</t>
+          <t>2026-08-25T20:55:01Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:42Z</t>
+          <t>2026-08-25T20:55:01Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:42Z</t>
+          <t>2026-08-25T20:55:01Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:42Z</t>
+          <t>2026-08-25T20:55:01Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:42Z</t>
+          <t>2026-08-25T20:55:01Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:42Z</t>
+          <t>2026-08-25T20:55:01Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:42Z</t>
+          <t>2026-08-25T20:55:01Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:42Z</t>
+          <t>2026-08-25T20:55:01Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:42Z</t>
+          <t>2026-08-25T20:55:01Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:42Z</t>
+          <t>2026-08-25T20:55:01Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:42Z</t>
+          <t>2026-08-25T20:55:01Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:42Z</t>
+          <t>2026-08-25T20:55:01Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:42Z</t>
+          <t>2026-08-25T20:55:01Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:42Z</t>
+          <t>2026-08-25T20:55:01Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:42Z</t>
+          <t>2026-08-25T20:55:01Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:42Z</t>
+          <t>2026-08-25T20:55:01Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:42Z</t>
+          <t>2026-08-25T20:55:01Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:42Z</t>
+          <t>2026-08-25T20:55:01Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-24T20:57:42Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-25T20:55:01Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:01Z</t>
+          <t>2026-08-26T23:55:47Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:01Z</t>
+          <t>2026-08-26T23:55:47Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:01Z</t>
+          <t>2026-08-26T23:55:47Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:01Z</t>
+          <t>2026-08-26T23:55:47Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:01Z</t>
+          <t>2026-08-26T23:55:47Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:01Z</t>
+          <t>2026-08-26T23:55:47Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:01Z</t>
+          <t>2026-08-26T23:55:47Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:01Z</t>
+          <t>2026-08-26T23:55:47Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:01Z</t>
+          <t>2026-08-26T23:55:47Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:01Z</t>
+          <t>2026-08-26T23:55:47Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:01Z</t>
+          <t>2026-08-26T23:55:47Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:01Z</t>
+          <t>2026-08-26T23:55:47Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:01Z</t>
+          <t>2026-08-26T23:55:47Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:01Z</t>
+          <t>2026-08-26T23:55:47Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:01Z</t>
+          <t>2026-08-26T23:55:47Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:01Z</t>
+          <t>2026-08-26T23:55:47Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:01Z</t>
+          <t>2026-08-26T23:55:47Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:01Z</t>
+          <t>2026-08-26T23:55:47Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:01Z</t>
+          <t>2026-08-26T23:55:47Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-25T20:55:01Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-26T23:55:47Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:47Z</t>
+          <t>2026-08-28T04:25:03Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:47Z</t>
+          <t>2026-08-28T04:25:03Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:47Z</t>
+          <t>2026-08-28T04:25:03Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:47Z</t>
+          <t>2026-08-28T04:25:03Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:47Z</t>
+          <t>2026-08-28T04:25:03Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:47Z</t>
+          <t>2026-08-28T04:25:03Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:47Z</t>
+          <t>2026-08-28T04:25:03Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:47Z</t>
+          <t>2026-08-28T04:25:03Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:47Z</t>
+          <t>2026-08-28T04:25:03Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:47Z</t>
+          <t>2026-08-28T04:25:03Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:47Z</t>
+          <t>2026-08-28T04:25:03Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:47Z</t>
+          <t>2026-08-28T04:25:03Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:47Z</t>
+          <t>2026-08-28T04:25:03Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:47Z</t>
+          <t>2026-08-28T04:25:03Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:47Z</t>
+          <t>2026-08-28T04:25:03Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:47Z</t>
+          <t>2026-08-28T04:25:03Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:47Z</t>
+          <t>2026-08-28T04:25:03Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:47Z</t>
+          <t>2026-08-28T04:25:03Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:47Z</t>
+          <t>2026-08-28T04:25:03Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-26T23:55:47Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-28T04:25:03Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:03Z</t>
+          <t>2026-08-29T02:52:51Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:03Z</t>
+          <t>2026-08-29T02:52:51Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:03Z</t>
+          <t>2026-08-29T02:52:51Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:03Z</t>
+          <t>2026-08-29T02:52:51Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:03Z</t>
+          <t>2026-08-29T02:52:51Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:03Z</t>
+          <t>2026-08-29T02:52:51Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:03Z</t>
+          <t>2026-08-29T02:52:51Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:03Z</t>
+          <t>2026-08-29T02:52:51Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:03Z</t>
+          <t>2026-08-29T02:52:51Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:03Z</t>
+          <t>2026-08-29T02:52:51Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:03Z</t>
+          <t>2026-08-29T02:52:51Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:03Z</t>
+          <t>2026-08-29T02:52:51Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:03Z</t>
+          <t>2026-08-29T02:52:51Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:03Z</t>
+          <t>2026-08-29T02:52:51Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:03Z</t>
+          <t>2026-08-29T02:52:51Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:03Z</t>
+          <t>2026-08-29T02:52:51Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:03Z</t>
+          <t>2026-08-29T02:52:51Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:03Z</t>
+          <t>2026-08-29T02:52:51Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:03Z</t>
+          <t>2026-08-29T02:52:51Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-28T04:25:03Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-29T02:52:51Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:51Z</t>
+          <t>2026-08-29T22:43:11Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:51Z</t>
+          <t>2026-08-29T22:43:11Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:51Z</t>
+          <t>2026-08-29T22:43:11Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:51Z</t>
+          <t>2026-08-29T22:43:11Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:51Z</t>
+          <t>2026-08-29T22:43:11Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:51Z</t>
+          <t>2026-08-29T22:43:11Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:51Z</t>
+          <t>2026-08-29T22:43:11Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:51Z</t>
+          <t>2026-08-29T22:43:11Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:51Z</t>
+          <t>2026-08-29T22:43:11Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:51Z</t>
+          <t>2026-08-29T22:43:11Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:51Z</t>
+          <t>2026-08-29T22:43:11Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:51Z</t>
+          <t>2026-08-29T22:43:11Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:51Z</t>
+          <t>2026-08-29T22:43:11Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:51Z</t>
+          <t>2026-08-29T22:43:11Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:51Z</t>
+          <t>2026-08-29T22:43:11Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:51Z</t>
+          <t>2026-08-29T22:43:11Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:51Z</t>
+          <t>2026-08-29T22:43:11Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:51Z</t>
+          <t>2026-08-29T22:43:11Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:51Z</t>
+          <t>2026-08-29T22:43:11Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-29T02:52:51Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-29T22:43:11Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:11Z</t>
+          <t>2026-08-30T22:52:50Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:11Z</t>
+          <t>2026-08-30T22:52:50Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:11Z</t>
+          <t>2026-08-30T22:52:50Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:11Z</t>
+          <t>2026-08-30T22:52:50Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:11Z</t>
+          <t>2026-08-30T22:52:50Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:11Z</t>
+          <t>2026-08-30T22:52:50Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:11Z</t>
+          <t>2026-08-30T22:52:50Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:11Z</t>
+          <t>2026-08-30T22:52:50Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:11Z</t>
+          <t>2026-08-30T22:52:50Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:11Z</t>
+          <t>2026-08-30T22:52:50Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:11Z</t>
+          <t>2026-08-30T22:52:50Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:11Z</t>
+          <t>2026-08-30T22:52:50Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:11Z</t>
+          <t>2026-08-30T22:52:50Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:11Z</t>
+          <t>2026-08-30T22:52:50Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:11Z</t>
+          <t>2026-08-30T22:52:50Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:11Z</t>
+          <t>2026-08-30T22:52:50Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:11Z</t>
+          <t>2026-08-30T22:52:50Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:11Z</t>
+          <t>2026-08-30T22:52:50Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:11Z</t>
+          <t>2026-08-30T22:52:50Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-29T22:43:11Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-30T22:52:50Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:50Z</t>
+          <t>2026-08-31T23:58:40Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:50Z</t>
+          <t>2026-08-31T23:58:40Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:50Z</t>
+          <t>2026-08-31T23:58:40Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:50Z</t>
+          <t>2026-08-31T23:58:40Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:50Z</t>
+          <t>2026-08-31T23:58:40Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:50Z</t>
+          <t>2026-08-31T23:58:40Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:50Z</t>
+          <t>2026-08-31T23:58:40Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:50Z</t>
+          <t>2026-08-31T23:58:40Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:50Z</t>
+          <t>2026-08-31T23:58:40Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:50Z</t>
+          <t>2026-08-31T23:58:40Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:50Z</t>
+          <t>2026-08-31T23:58:40Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:50Z</t>
+          <t>2026-08-31T23:58:40Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:50Z</t>
+          <t>2026-08-31T23:58:40Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:50Z</t>
+          <t>2026-08-31T23:58:40Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:50Z</t>
+          <t>2026-08-31T23:58:40Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:50Z</t>
+          <t>2026-08-31T23:58:40Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:50Z</t>
+          <t>2026-08-31T23:58:40Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:50Z</t>
+          <t>2026-08-31T23:58:40Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:50Z</t>
+          <t>2026-08-31T23:58:40Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-30T22:52:50Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-31T23:58:40Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:40Z</t>
+          <t>2026-09-01T22:43:22Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:40Z</t>
+          <t>2026-09-01T22:43:22Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:40Z</t>
+          <t>2026-09-01T22:43:22Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:40Z</t>
+          <t>2026-09-01T22:43:22Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:40Z</t>
+          <t>2026-09-01T22:43:22Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:40Z</t>
+          <t>2026-09-01T22:43:22Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:40Z</t>
+          <t>2026-09-01T22:43:22Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:40Z</t>
+          <t>2026-09-01T22:43:22Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:40Z</t>
+          <t>2026-09-01T22:43:22Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:40Z</t>
+          <t>2026-09-01T22:43:22Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:40Z</t>
+          <t>2026-09-01T22:43:22Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:40Z</t>
+          <t>2026-09-01T22:43:22Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:40Z</t>
+          <t>2026-09-01T22:43:22Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:40Z</t>
+          <t>2026-09-01T22:43:22Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:40Z</t>
+          <t>2026-09-01T22:43:22Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:40Z</t>
+          <t>2026-09-01T22:43:22Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:40Z</t>
+          <t>2026-09-01T22:43:22Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:40Z</t>
+          <t>2026-09-01T22:43:22Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:40Z</t>
+          <t>2026-09-01T22:43:22Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-08-31T23:58:40Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-01T22:43:22Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:22Z</t>
+          <t>2026-09-02T17:10:07Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:22Z</t>
+          <t>2026-09-02T17:10:07Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:22Z</t>
+          <t>2026-09-02T17:10:07Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:22Z</t>
+          <t>2026-09-02T17:10:07Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:22Z</t>
+          <t>2026-09-02T17:10:07Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:22Z</t>
+          <t>2026-09-02T17:10:07Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:22Z</t>
+          <t>2026-09-02T17:10:07Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:22Z</t>
+          <t>2026-09-02T17:10:07Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:22Z</t>
+          <t>2026-09-02T17:10:07Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:22Z</t>
+          <t>2026-09-02T17:10:07Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:22Z</t>
+          <t>2026-09-02T17:10:07Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:22Z</t>
+          <t>2026-09-02T17:10:07Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:22Z</t>
+          <t>2026-09-02T17:10:07Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:22Z</t>
+          <t>2026-09-02T17:10:07Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:22Z</t>
+          <t>2026-09-02T17:10:07Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:22Z</t>
+          <t>2026-09-02T17:10:07Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:22Z</t>
+          <t>2026-09-02T17:10:07Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:22Z</t>
+          <t>2026-09-02T17:10:07Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:22Z</t>
+          <t>2026-09-02T17:10:07Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-01T22:43:22Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-02T17:10:07Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:07Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:07Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:07Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:07Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:07Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:07Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:07Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:07Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:07Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:07Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:07Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:07Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:07Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:07Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:07Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:07Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:07Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:07Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:07Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-02T17:10:07Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-02T22:45:38Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:48Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:48Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:48Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:48Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:48Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:48Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:48Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:48Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:48Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:48Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:48Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-02T22:45:38Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-03T22:43:48Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:48Z</t>
+          <t>2026-09-04T22:26:50Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:48Z</t>
+          <t>2026-09-04T22:26:50Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:48Z</t>
+          <t>2026-09-04T22:26:50Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:48Z</t>
+          <t>2026-09-04T22:26:50Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:48Z</t>
+          <t>2026-09-04T22:26:50Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:48Z</t>
+          <t>2026-09-04T22:26:50Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:48Z</t>
+          <t>2026-09-04T22:26:50Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:48Z</t>
+          <t>2026-09-04T22:26:50Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:48Z</t>
+          <t>2026-09-04T22:26:50Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:48Z</t>
+          <t>2026-09-04T22:26:50Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:48Z</t>
+          <t>2026-09-04T22:26:50Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:48Z</t>
+          <t>2026-09-04T22:26:50Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:48Z</t>
+          <t>2026-09-04T22:26:50Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:48Z</t>
+          <t>2026-09-04T22:26:50Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:48Z</t>
+          <t>2026-09-04T22:26:50Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:48Z</t>
+          <t>2026-09-04T22:26:50Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:48Z</t>
+          <t>2026-09-04T22:26:50Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:48Z</t>
+          <t>2026-09-04T22:26:50Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:48Z</t>
+          <t>2026-09-04T22:26:50Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-03T22:43:48Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-04T22:26:50Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:50Z</t>
+          <t>2026-09-05T22:09:17Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:50Z</t>
+          <t>2026-09-05T22:09:17Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:50Z</t>
+          <t>2026-09-05T22:09:17Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:50Z</t>
+          <t>2026-09-05T22:09:17Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:50Z</t>
+          <t>2026-09-05T22:09:17Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:50Z</t>
+          <t>2026-09-05T22:09:17Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:50Z</t>
+          <t>2026-09-05T22:09:17Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:50Z</t>
+          <t>2026-09-05T22:09:17Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:50Z</t>
+          <t>2026-09-05T22:09:17Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:50Z</t>
+          <t>2026-09-05T22:09:17Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:50Z</t>
+          <t>2026-09-05T22:09:17Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:50Z</t>
+          <t>2026-09-05T22:09:17Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:50Z</t>
+          <t>2026-09-05T22:09:17Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:50Z</t>
+          <t>2026-09-05T22:09:17Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:50Z</t>
+          <t>2026-09-05T22:09:17Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:50Z</t>
+          <t>2026-09-05T22:09:17Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:50Z</t>
+          <t>2026-09-05T22:09:17Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:50Z</t>
+          <t>2026-09-05T22:09:17Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:50Z</t>
+          <t>2026-09-05T22:09:17Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-04T22:26:50Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-05T22:09:17Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:17Z</t>
+          <t>2026-09-06T22:12:29Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:17Z</t>
+          <t>2026-09-06T22:12:29Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:17Z</t>
+          <t>2026-09-06T22:12:29Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:17Z</t>
+          <t>2026-09-06T22:12:29Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:17Z</t>
+          <t>2026-09-06T22:12:29Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:17Z</t>
+          <t>2026-09-06T22:12:29Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:17Z</t>
+          <t>2026-09-06T22:12:29Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:17Z</t>
+          <t>2026-09-06T22:12:29Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:17Z</t>
+          <t>2026-09-06T22:12:29Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:17Z</t>
+          <t>2026-09-06T22:12:29Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:17Z</t>
+          <t>2026-09-06T22:12:29Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:17Z</t>
+          <t>2026-09-06T22:12:29Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:17Z</t>
+          <t>2026-09-06T22:12:29Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:17Z</t>
+          <t>2026-09-06T22:12:29Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:17Z</t>
+          <t>2026-09-06T22:12:29Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:17Z</t>
+          <t>2026-09-06T22:12:29Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:17Z</t>
+          <t>2026-09-06T22:12:29Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:17Z</t>
+          <t>2026-09-06T22:12:29Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:17Z</t>
+          <t>2026-09-06T22:12:29Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-05T22:09:17Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-06T22:12:29Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:29Z</t>
+          <t>2026-09-07T18:15:17Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:29Z</t>
+          <t>2026-09-07T18:15:17Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:29Z</t>
+          <t>2026-09-07T18:15:17Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:29Z</t>
+          <t>2026-09-07T18:15:17Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:29Z</t>
+          <t>2026-09-07T18:15:17Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:29Z</t>
+          <t>2026-09-07T18:15:17Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:29Z</t>
+          <t>2026-09-07T18:15:17Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:29Z</t>
+          <t>2026-09-07T18:15:17Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:29Z</t>
+          <t>2026-09-07T18:15:17Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:29Z</t>
+          <t>2026-09-07T18:15:17Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:29Z</t>
+          <t>2026-09-07T18:15:17Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:29Z</t>
+          <t>2026-09-07T18:15:17Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:29Z</t>
+          <t>2026-09-07T18:15:17Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:29Z</t>
+          <t>2026-09-07T18:15:17Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:29Z</t>
+          <t>2026-09-07T18:15:17Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:29Z</t>
+          <t>2026-09-07T18:15:17Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:29Z</t>
+          <t>2026-09-07T18:15:17Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:29Z</t>
+          <t>2026-09-07T18:15:17Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:29Z</t>
+          <t>2026-09-07T18:15:17Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-06T22:12:29Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-07T18:15:17Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:17Z</t>
+          <t>2026-09-07T22:56:43Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:17Z</t>
+          <t>2026-09-07T22:56:43Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:17Z</t>
+          <t>2026-09-07T22:56:43Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:17Z</t>
+          <t>2026-09-07T22:56:43Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:17Z</t>
+          <t>2026-09-07T22:56:43Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:17Z</t>
+          <t>2026-09-07T22:56:43Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:17Z</t>
+          <t>2026-09-07T22:56:43Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:17Z</t>
+          <t>2026-09-07T22:56:43Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:17Z</t>
+          <t>2026-09-07T22:56:43Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:17Z</t>
+          <t>2026-09-07T22:56:43Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:17Z</t>
+          <t>2026-09-07T22:56:43Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:17Z</t>
+          <t>2026-09-07T22:56:43Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:17Z</t>
+          <t>2026-09-07T22:56:43Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:17Z</t>
+          <t>2026-09-07T22:56:43Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:17Z</t>
+          <t>2026-09-07T22:56:43Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:17Z</t>
+          <t>2026-09-07T22:56:43Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:17Z</t>
+          <t>2026-09-07T22:56:43Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:17Z</t>
+          <t>2026-09-07T22:56:43Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:17Z</t>
+          <t>2026-09-07T22:56:43Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-07T18:15:17Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-07T22:56:43Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:43Z</t>
+          <t>2026-09-08T22:51:28Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:43Z</t>
+          <t>2026-09-08T22:51:28Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:43Z</t>
+          <t>2026-09-08T22:51:28Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:43Z</t>
+          <t>2026-09-08T22:51:28Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:43Z</t>
+          <t>2026-09-08T22:51:28Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:43Z</t>
+          <t>2026-09-08T22:51:28Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:43Z</t>
+          <t>2026-09-08T22:51:28Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:43Z</t>
+          <t>2026-09-08T22:51:28Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:43Z</t>
+          <t>2026-09-08T22:51:28Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:43Z</t>
+          <t>2026-09-08T22:51:28Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:43Z</t>
+          <t>2026-09-08T22:51:28Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:43Z</t>
+          <t>2026-09-08T22:51:28Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:43Z</t>
+          <t>2026-09-08T22:51:28Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:43Z</t>
+          <t>2026-09-08T22:51:28Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:43Z</t>
+          <t>2026-09-08T22:51:28Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:43Z</t>
+          <t>2026-09-08T22:51:28Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:43Z</t>
+          <t>2026-09-08T22:51:28Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:43Z</t>
+          <t>2026-09-08T22:51:28Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:43Z</t>
+          <t>2026-09-08T22:51:28Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-07T22:56:43Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-08T22:51:28Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:28Z</t>
+          <t>2026-09-09T22:40:33Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:28Z</t>
+          <t>2026-09-09T22:40:33Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:28Z</t>
+          <t>2026-09-09T22:40:33Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:28Z</t>
+          <t>2026-09-09T22:40:33Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:28Z</t>
+          <t>2026-09-09T22:40:33Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:28Z</t>
+          <t>2026-09-09T22:40:33Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:28Z</t>
+          <t>2026-09-09T22:40:33Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:28Z</t>
+          <t>2026-09-09T22:40:33Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:28Z</t>
+          <t>2026-09-09T22:40:33Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:28Z</t>
+          <t>2026-09-09T22:40:33Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:28Z</t>
+          <t>2026-09-09T22:40:33Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:28Z</t>
+          <t>2026-09-09T22:40:33Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:28Z</t>
+          <t>2026-09-09T22:40:33Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:28Z</t>
+          <t>2026-09-09T22:40:33Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:28Z</t>
+          <t>2026-09-09T22:40:33Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:28Z</t>
+          <t>2026-09-09T22:40:33Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:28Z</t>
+          <t>2026-09-09T22:40:33Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:28Z</t>
+          <t>2026-09-09T22:40:33Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:28Z</t>
+          <t>2026-09-09T22:40:33Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-08T22:51:28Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-09T22:40:33Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:33Z</t>
+          <t>2026-09-10T22:42:28Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:33Z</t>
+          <t>2026-09-10T22:42:28Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:33Z</t>
+          <t>2026-09-10T22:42:28Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:33Z</t>
+          <t>2026-09-10T22:42:28Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:33Z</t>
+          <t>2026-09-10T22:42:28Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:33Z</t>
+          <t>2026-09-10T22:42:28Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:33Z</t>
+          <t>2026-09-10T22:42:28Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:33Z</t>
+          <t>2026-09-10T22:42:28Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:33Z</t>
+          <t>2026-09-10T22:42:28Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:33Z</t>
+          <t>2026-09-10T22:42:28Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:33Z</t>
+          <t>2026-09-10T22:42:28Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:33Z</t>
+          <t>2026-09-10T22:42:28Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:33Z</t>
+          <t>2026-09-10T22:42:28Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:33Z</t>
+          <t>2026-09-10T22:42:28Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:33Z</t>
+          <t>2026-09-10T22:42:28Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:33Z</t>
+          <t>2026-09-10T22:42:28Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:33Z</t>
+          <t>2026-09-10T22:42:28Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:33Z</t>
+          <t>2026-09-10T22:42:28Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:33Z</t>
+          <t>2026-09-10T22:42:28Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-09T22:40:33Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-10T22:42:28Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:28Z</t>
+          <t>2026-09-11T22:42:44Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:28Z</t>
+          <t>2026-09-11T22:42:44Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:28Z</t>
+          <t>2026-09-11T22:42:44Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:28Z</t>
+          <t>2026-09-11T22:42:44Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:28Z</t>
+          <t>2026-09-11T22:42:44Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:28Z</t>
+          <t>2026-09-11T22:42:44Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:28Z</t>
+          <t>2026-09-11T22:42:44Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:28Z</t>
+          <t>2026-09-11T22:42:44Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:28Z</t>
+          <t>2026-09-11T22:42:44Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:28Z</t>
+          <t>2026-09-11T22:42:44Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:28Z</t>
+          <t>2026-09-11T22:42:44Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:28Z</t>
+          <t>2026-09-11T22:42:44Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:28Z</t>
+          <t>2026-09-11T22:42:44Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:28Z</t>
+          <t>2026-09-11T22:42:44Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:28Z</t>
+          <t>2026-09-11T22:42:44Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:28Z</t>
+          <t>2026-09-11T22:42:44Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:28Z</t>
+          <t>2026-09-11T22:42:44Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:28Z</t>
+          <t>2026-09-11T22:42:44Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:28Z</t>
+          <t>2026-09-11T22:42:44Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-10T22:42:28Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-11T22:42:44Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:44Z</t>
+          <t>2026-09-12T16:18:27Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:44Z</t>
+          <t>2026-09-12T16:18:27Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:44Z</t>
+          <t>2026-09-12T16:18:27Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:44Z</t>
+          <t>2026-09-12T16:18:27Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:44Z</t>
+          <t>2026-09-12T16:18:27Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:44Z</t>
+          <t>2026-09-12T16:18:27Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:44Z</t>
+          <t>2026-09-12T16:18:27Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:44Z</t>
+          <t>2026-09-12T16:18:27Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:44Z</t>
+          <t>2026-09-12T16:18:27Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:44Z</t>
+          <t>2026-09-12T16:18:27Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:44Z</t>
+          <t>2026-09-12T16:18:27Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:44Z</t>
+          <t>2026-09-12T16:18:27Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:44Z</t>
+          <t>2026-09-12T16:18:27Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:44Z</t>
+          <t>2026-09-12T16:18:27Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:44Z</t>
+          <t>2026-09-12T16:18:27Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:44Z</t>
+          <t>2026-09-12T16:18:27Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:44Z</t>
+          <t>2026-09-12T16:18:27Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:44Z</t>
+          <t>2026-09-12T16:18:27Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:44Z</t>
+          <t>2026-09-12T16:18:27Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-11T22:42:44Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-12T16:18:27Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_real_anual.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:27Z</t>
+          <t>2026-09-12T22:27:00Z</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:27Z</t>
+          <t>2026-09-12T22:27:00Z</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:27Z</t>
+          <t>2026-09-12T22:27:00Z</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:27Z</t>
+          <t>2026-09-12T22:27:00Z</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:27Z</t>
+          <t>2026-09-12T22:27:00Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:27Z</t>
+          <t>2026-09-12T22:27:00Z</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:27Z</t>
+          <t>2026-09-12T22:27:00Z</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:27Z</t>
+          <t>2026-09-12T22:27:00Z</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:27Z</t>
+          <t>2026-09-12T22:27:00Z</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:27Z</t>
+          <t>2026-09-12T22:27:00Z</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:27Z</t>
+          <t>2026-09-12T22:27:00Z</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:27Z</t>
+          <t>2026-09-12T22:27:00Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:27Z</t>
+          <t>2026-09-12T22:27:00Z</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:27Z</t>
+          <t>2026-09-12T22:27:00Z</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:27Z</t>
+          <t>2026-09-12T22:27:00Z</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:27Z</t>
+          <t>2026-09-12T22:27:00Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:27Z</t>
+          <t>2026-09-12T22:27:00Z</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:27Z</t>
+          <t>2026-09-12T22:27:00Z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:27Z</t>
+          <t>2026-09-12T22:27:00Z</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-12T16:18:27Z"}</t>
+          <t>{"year": 2025, "annual_real_gdp_growth_pct": 9.012862992888856, "unit": "Variación porcentual anual a precios de 2007", "frequency": "annual", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-12T22:27:00Z"}</t>
         </is>
       </c>
     </row>
